--- a/Tables/Table2.xlsx
+++ b/Tables/Table2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
   <si>
     <t>level</t>
   </si>
@@ -61,196 +61,211 @@
     <t>White</t>
   </si>
   <si>
-    <t>121936</t>
-  </si>
-  <si>
-    <t>57.32 (7.94)</t>
-  </si>
-  <si>
-    <t>66491 (54.5)</t>
-  </si>
-  <si>
-    <t>55445 (45.5)</t>
-  </si>
-  <si>
-    <t>16.89 (13.85)</t>
+    <t>74148</t>
+  </si>
+  <si>
+    <t>57.26 (7.97)</t>
+  </si>
+  <si>
+    <t>40386 (54.5)</t>
+  </si>
+  <si>
+    <t>33762 (45.5)</t>
+  </si>
+  <si>
+    <t>16.87 (13.85)</t>
+  </si>
+  <si>
+    <t>27.55 (4.81)</t>
+  </si>
+  <si>
+    <t>74148 (100.0)</t>
+  </si>
+  <si>
+    <t>251565</t>
+  </si>
+  <si>
+    <t>57.31 (7.96)</t>
+  </si>
+  <si>
+    <t>136925 (54.4)</t>
+  </si>
+  <si>
+    <t>114640 (45.6)</t>
+  </si>
+  <si>
+    <t>16.90 (13.84)</t>
+  </si>
+  <si>
+    <t>27.54 (4.81)</t>
+  </si>
+  <si>
+    <t>251565 (100.0)</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>139668</t>
+  </si>
+  <si>
+    <t>57.31 (7.95)</t>
+  </si>
+  <si>
+    <t>76061 (54.5)</t>
+  </si>
+  <si>
+    <t>63607 (45.5)</t>
+  </si>
+  <si>
+    <t>16.87 (13.83)</t>
+  </si>
+  <si>
+    <t>27.54 (4.82)</t>
+  </si>
+  <si>
+    <t>139668 (100.0)</t>
+  </si>
+  <si>
+    <t>186045</t>
+  </si>
+  <si>
+    <t>57.29 (7.97)</t>
+  </si>
+  <si>
+    <t>101250 (54.4)</t>
+  </si>
+  <si>
+    <t>84795 (45.6)</t>
+  </si>
+  <si>
+    <t>16.91 (13.85)</t>
+  </si>
+  <si>
+    <t>27.54 (4.80)</t>
+  </si>
+  <si>
+    <t>186045 (100.0)</t>
+  </si>
+  <si>
+    <t>54635</t>
+  </si>
+  <si>
+    <t>57.25 (7.98)</t>
+  </si>
+  <si>
+    <t>29741 (54.4)</t>
+  </si>
+  <si>
+    <t>24894 (45.6)</t>
+  </si>
+  <si>
+    <t>16.90 (13.86)</t>
+  </si>
+  <si>
+    <t>27.55 (4.78)</t>
+  </si>
+  <si>
+    <t>54635 (100.0)</t>
+  </si>
+  <si>
+    <t>271078</t>
+  </si>
+  <si>
+    <t>147570 (54.4)</t>
+  </si>
+  <si>
+    <t>123508 (45.6)</t>
+  </si>
+  <si>
+    <t>16.89 (13.84)</t>
+  </si>
+  <si>
+    <t>271078 (100.0)</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>279123</t>
+  </si>
+  <si>
+    <t>57.30 (7.96)</t>
+  </si>
+  <si>
+    <t>151989 (54.5)</t>
+  </si>
+  <si>
+    <t>127134 (45.5)</t>
+  </si>
+  <si>
+    <t>16.88 (13.84)</t>
+  </si>
+  <si>
+    <t>279123 (100.0)</t>
+  </si>
+  <si>
+    <t>46590</t>
+  </si>
+  <si>
+    <t>57.27 (7.98)</t>
+  </si>
+  <si>
+    <t>25322 (54.4)</t>
+  </si>
+  <si>
+    <t>21268 (45.6)</t>
+  </si>
+  <si>
+    <t>16.99 (13.83)</t>
   </si>
   <si>
     <t>27.55 (4.83)</t>
   </si>
   <si>
-    <t>121936 (100.0)</t>
-  </si>
-  <si>
-    <t>203777</t>
+    <t>46590 (100.0)</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>159399</t>
+  </si>
+  <si>
+    <t>86697 (54.4)</t>
+  </si>
+  <si>
+    <t>72702 (45.6)</t>
+  </si>
+  <si>
+    <t>16.89 (13.83)</t>
+  </si>
+  <si>
+    <t>27.55 (4.82)</t>
+  </si>
+  <si>
+    <t>159399 (100.0)</t>
+  </si>
+  <si>
+    <t>166314</t>
   </si>
   <si>
     <t>57.28 (7.97)</t>
-  </si>
-  <si>
-    <t>110820 (54.4)</t>
-  </si>
-  <si>
-    <t>92957 (45.6)</t>
-  </si>
-  <si>
-    <t>16.89 (13.84)</t>
-  </si>
-  <si>
-    <t>27.54 (4.80)</t>
-  </si>
-  <si>
-    <t>203777 (100.0)</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>&lt;0.001</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>139668</t>
-  </si>
-  <si>
-    <t>57.31 (7.95)</t>
-  </si>
-  <si>
-    <t>76061 (54.5)</t>
-  </si>
-  <si>
-    <t>63607 (45.5)</t>
-  </si>
-  <si>
-    <t>16.87 (13.83)</t>
-  </si>
-  <si>
-    <t>27.54 (4.82)</t>
-  </si>
-  <si>
-    <t>139668 (100.0)</t>
-  </si>
-  <si>
-    <t>186045</t>
-  </si>
-  <si>
-    <t>57.29 (7.97)</t>
-  </si>
-  <si>
-    <t>101250 (54.4)</t>
-  </si>
-  <si>
-    <t>84795 (45.6)</t>
-  </si>
-  <si>
-    <t>16.91 (13.85)</t>
-  </si>
-  <si>
-    <t>186045 (100.0)</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>128753</t>
-  </si>
-  <si>
-    <t>57.32 (7.95)</t>
-  </si>
-  <si>
-    <t>70057 (54.4)</t>
-  </si>
-  <si>
-    <t>58696 (45.6)</t>
-  </si>
-  <si>
-    <t>16.90 (13.84)</t>
-  </si>
-  <si>
-    <t>128753 (100.0)</t>
-  </si>
-  <si>
-    <t>196960</t>
-  </si>
-  <si>
-    <t>107254 (54.5)</t>
-  </si>
-  <si>
-    <t>89706 (45.5)</t>
-  </si>
-  <si>
-    <t>196960 (100.0)</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>279123</t>
-  </si>
-  <si>
-    <t>57.30 (7.96)</t>
-  </si>
-  <si>
-    <t>151989 (54.5)</t>
-  </si>
-  <si>
-    <t>127134 (45.5)</t>
-  </si>
-  <si>
-    <t>16.88 (13.84)</t>
-  </si>
-  <si>
-    <t>27.54 (4.81)</t>
-  </si>
-  <si>
-    <t>279123 (100.0)</t>
-  </si>
-  <si>
-    <t>46590</t>
-  </si>
-  <si>
-    <t>57.27 (7.98)</t>
-  </si>
-  <si>
-    <t>25322 (54.4)</t>
-  </si>
-  <si>
-    <t>21268 (45.6)</t>
-  </si>
-  <si>
-    <t>16.99 (13.83)</t>
-  </si>
-  <si>
-    <t>46590 (100.0)</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>159399</t>
-  </si>
-  <si>
-    <t>86697 (54.4)</t>
-  </si>
-  <si>
-    <t>72702 (45.6)</t>
-  </si>
-  <si>
-    <t>16.89 (13.83)</t>
-  </si>
-  <si>
-    <t>27.55 (4.82)</t>
-  </si>
-  <si>
-    <t>159399 (100.0)</t>
-  </si>
-  <si>
-    <t>166314</t>
   </si>
   <si>
     <t>90614 (54.5)</t>
@@ -474,7 +489,7 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -510,10 +525,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -527,13 +542,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -544,13 +559,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -561,10 +576,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -578,13 +593,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -595,13 +610,13 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -612,13 +627,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -654,10 +669,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -671,13 +686,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -688,13 +703,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -705,10 +720,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -722,13 +737,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -739,10 +754,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -756,13 +771,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -798,10 +813,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -815,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
@@ -832,13 +847,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -849,10 +864,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -866,13 +881,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -883,13 +898,13 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -900,13 +915,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -942,10 +957,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -959,10 +974,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -976,13 +991,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -993,10 +1008,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -1010,13 +1025,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1027,13 +1042,13 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -1044,13 +1059,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1086,10 +1101,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1103,13 +1118,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -1120,13 +1135,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -1137,10 +1152,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -1154,13 +1169,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1171,13 +1186,13 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1188,13 +1203,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
